--- a/uploads/teacher_subject_mapping.xlsx
+++ b/uploads/teacher_subject_mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4A69F6E-4040-4114-9857-D56A87DCCA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7883F15-D4BA-4473-917D-194AB99C340E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{849BA79E-C918-47C8-A74D-3C07CE7264D9}"/>
+    <workbookView xWindow="2196" yWindow="2196" windowWidth="17280" windowHeight="8880" xr2:uid="{849BA79E-C918-47C8-A74D-3C07CE7264D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="46">
   <si>
     <t>faculty</t>
   </si>
@@ -109,9 +109,6 @@
   </si>
   <si>
     <t>ACTIVITY HOUR</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ACTIVITY HOUR</t>
   </si>
   <si>
     <t>IOT</t>
@@ -546,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EA82E80-2D75-4B50-B5E1-CCF49967776B}">
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -562,62 +559,62 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s">
         <v>43</v>
       </c>
-      <c r="B6" t="s">
-        <v>44</v>
-      </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -628,7 +625,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -636,10 +633,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -650,7 +647,7 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -661,7 +658,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -669,10 +666,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -683,7 +680,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -691,10 +688,10 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -705,7 +702,7 @@
         <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -716,7 +713,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -724,10 +721,10 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -735,10 +732,10 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -749,7 +746,7 @@
         <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -760,7 +757,7 @@
         <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -768,10 +765,10 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -782,7 +779,7 @@
         <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -793,7 +790,7 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -801,10 +798,10 @@
         <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -812,10 +809,10 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -826,7 +823,7 @@
         <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -834,21 +831,21 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C27" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -856,10 +853,10 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C28" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -867,10 +864,10 @@
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C29" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -878,21 +875,21 @@
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C30" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -900,10 +897,10 @@
         <v>23</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -911,7 +908,7 @@
         <v>23</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="C33" t="s">
         <v>36</v>
@@ -922,10 +919,10 @@
         <v>23</v>
       </c>
       <c r="B34" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -933,76 +930,76 @@
         <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C35" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C37" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B38" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C38" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C40" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="C41" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -1010,7 +1007,7 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C42" t="s">
         <v>37</v>
@@ -1018,10 +1015,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="C43" t="s">
         <v>38</v>
@@ -1029,46 +1026,35 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="C44" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" t="s">
         <v>30</v>
       </c>
-      <c r="B45" t="s">
-        <v>40</v>
-      </c>
       <c r="C45" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C46" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>46</v>
-      </c>
-      <c r="B47" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/teacher_subject_mapping.xlsx
+++ b/uploads/teacher_subject_mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7883F15-D4BA-4473-917D-194AB99C340E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6580EE5C-5B98-4C03-A070-D859D3F1C005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2196" yWindow="2196" windowWidth="17280" windowHeight="8880" xr2:uid="{849BA79E-C918-47C8-A74D-3C07CE7264D9}"/>
+    <workbookView xWindow="2892" yWindow="2892" windowWidth="17280" windowHeight="8880" xr2:uid="{849BA79E-C918-47C8-A74D-3C07CE7264D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="45">
   <si>
     <t>faculty</t>
   </si>
@@ -108,9 +108,6 @@
     <t>SWC</t>
   </si>
   <si>
-    <t>ACTIVITY HOUR</t>
-  </si>
-  <si>
     <t>IOT</t>
   </si>
   <si>
@@ -168,10 +165,10 @@
     <t>IT W/S/PHY LAB</t>
   </si>
   <si>
-    <t>CP/IT W/S</t>
-  </si>
-  <si>
     <t>SHC</t>
+  </si>
+  <si>
+    <t>CP /ITLAB W/S</t>
   </si>
 </sst>
 </file>
@@ -543,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EA82E80-2D75-4B50-B5E1-CCF49967776B}">
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -559,62 +556,62 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
         <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s">
         <v>42</v>
       </c>
-      <c r="B6" t="s">
-        <v>43</v>
-      </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -625,7 +622,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -633,10 +630,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -647,7 +644,7 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -658,7 +655,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -666,10 +663,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -680,7 +677,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -688,10 +685,10 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -702,7 +699,7 @@
         <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -713,7 +710,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -721,10 +718,10 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -732,10 +729,10 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -746,7 +743,7 @@
         <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -757,7 +754,7 @@
         <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -765,10 +762,10 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -779,7 +776,7 @@
         <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -790,7 +787,7 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -801,7 +798,7 @@
         <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -812,7 +809,7 @@
         <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -823,7 +820,7 @@
         <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -831,10 +828,10 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -845,7 +842,7 @@
         <v>20</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -856,7 +853,7 @@
         <v>22</v>
       </c>
       <c r="C28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -867,7 +864,7 @@
         <v>21</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -875,10 +872,10 @@
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -889,7 +886,7 @@
         <v>44</v>
       </c>
       <c r="C31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -897,10 +894,10 @@
         <v>23</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -911,7 +908,7 @@
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -922,73 +919,73 @@
         <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -996,7 +993,7 @@
         <v>28</v>
       </c>
       <c r="B41" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C41" t="s">
         <v>36</v>
@@ -1004,10 +1001,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B42" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C42" t="s">
         <v>37</v>
@@ -1015,46 +1012,35 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B43" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="C43" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
         <v>29</v>
       </c>
-      <c r="B44" t="s">
-        <v>39</v>
-      </c>
       <c r="C44" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>45</v>
-      </c>
-      <c r="B46" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
